--- a/dup_project/01_Процессы/ДУП_метрики_процессов.xlsx
+++ b/dup_project/01_Процессы/ДУП_метрики_процессов.xlsx
@@ -36915,12 +36915,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Владелец закреплён за замом по строительству и реализации, но должность вводится приказом, а паспорта процесса нет</t>
+          <t>Владелец закреплён за замом по строительству и реализации, но паспорта процесса нет: границы, вход и выход фазы нигде не описаны</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Издать приказ о разделении заместителей, утвердить паспорт процесса</t>
+          <t>Утвердить паспорт процесса реализации: границы, вход, выход и показатели</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -37620,12 +37620,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Владелец закреплён за главным менеджером проектов, но право останавливать проект по результатам аудита приказом не закреплено</t>
+          <t>Владелец и его право останавливать проект по результатам аудита закреплены, но паспорта процесса нет</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Закрепить полномочия ПМО приказом и утвердить паспорт процесса</t>
+          <t>Утвердить положение о контроле качества проектных данных и паспорт процесса</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
